--- a/ToxCast_model/experiments/prediction/DART_MTL_251228/DART_MTL_seed0train/score_seed0train.xlsx
+++ b/ToxCast_model/experiments/prediction/DART_MTL_251228/DART_MTL_seed0train/score_seed0train.xlsx
@@ -5322,7 +5322,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>0.9990222043456957</v>
+        <v>0.9990222043456954</v>
       </c>
       <c r="E140" t="n">
         <v>0.9875634102438227</v>
@@ -6162,7 +6162,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>0.9997153289013395</v>
+        <v>0.9997153289013394</v>
       </c>
       <c r="E164" t="n">
         <v>0.9941089837997055</v>
@@ -6407,7 +6407,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>0.9959806063721919</v>
+        <v>0.9959806063721921</v>
       </c>
       <c r="E171" t="n">
         <v>0.9896701099633456</v>
@@ -7037,7 +7037,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>0.9962739015942305</v>
+        <v>0.9962739015942303</v>
       </c>
       <c r="E189" t="n">
         <v>0.9726722304041892</v>
@@ -7072,7 +7072,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>0.9995322248844655</v>
+        <v>0.9995322248844656</v>
       </c>
       <c r="E190" t="n">
         <v>0.9942382647008982</v>
@@ -8122,7 +8122,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>0.9783395803672028</v>
+        <v>0.978339580367203</v>
       </c>
       <c r="E220" t="n">
         <v>0.9563478840386538</v>
@@ -8717,7 +8717,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>0.9949967157548871</v>
+        <v>0.994996715754887</v>
       </c>
       <c r="E237" t="n">
         <v>0.9644902634593356</v>
